--- a/site/downloads/annual/cvd/latest/workbook/workbook_cvd_annual_tabulations.xlsx
+++ b/site/downloads/annual/cvd/latest/workbook/workbook_cvd_annual_tabulations.xlsx
@@ -952,13 +952,16 @@
     <t>Crude rate</t>
   </si>
   <si>
+    <t>154.4</t>
+  </si>
+  <si>
+    <t>155.9</t>
+  </si>
+  <si>
     <t>157.2</t>
   </si>
   <si>
-    <t>154.4</t>
-  </si>
-  <si>
-    <t>155.9</t>
+    <t>197.8</t>
   </si>
   <si>
     <t>211.1</t>
@@ -967,27 +970,24 @@
     <t>223.3</t>
   </si>
   <si>
-    <t>197.8</t>
+    <t>50.2</t>
   </si>
   <si>
     <t>41.7</t>
   </si>
   <si>
-    <t>50.2</t>
-  </si>
-  <si>
     <t>45.8</t>
   </si>
   <si>
+    <t>125.0</t>
+  </si>
+  <si>
+    <t>125.5</t>
+  </si>
+  <si>
     <t>124.5</t>
   </si>
   <si>
-    <t>125.5</t>
-  </si>
-  <si>
-    <t>125.0</t>
-  </si>
-  <si>
     <t>139.4</t>
   </si>
   <si>
@@ -1009,102 +1009,102 @@
     <t>87.4</t>
   </si>
   <si>
+    <t>106.5</t>
+  </si>
+  <si>
     <t>127.3</t>
   </si>
   <si>
-    <t>106.5</t>
-  </si>
-  <si>
     <t>147.3</t>
   </si>
   <si>
+    <t>143.4</t>
+  </si>
+  <si>
     <t>139.8</t>
   </si>
   <si>
-    <t>143.4</t>
+    <t>194.1</t>
+  </si>
+  <si>
+    <t>222.1</t>
   </si>
   <si>
     <t>208.7</t>
   </si>
   <si>
-    <t>194.1</t>
-  </si>
-  <si>
-    <t>222.1</t>
+    <t>68.7</t>
+  </si>
+  <si>
+    <t>67.5</t>
   </si>
   <si>
     <t>66.4</t>
   </si>
   <si>
-    <t>67.5</t>
-  </si>
-  <si>
-    <t>68.7</t>
+    <t>139.1</t>
+  </si>
+  <si>
+    <t>153.3</t>
   </si>
   <si>
     <t>145.9</t>
   </si>
   <si>
-    <t>139.1</t>
-  </si>
-  <si>
-    <t>153.3</t>
+    <t>200.3</t>
+  </si>
+  <si>
+    <t>191.9</t>
   </si>
   <si>
     <t>195.9</t>
   </si>
   <si>
-    <t>200.3</t>
-  </si>
-  <si>
-    <t>191.9</t>
+    <t>246.2</t>
   </si>
   <si>
     <t>249.9</t>
   </si>
   <si>
-    <t>246.2</t>
-  </si>
-  <si>
     <t>253.4</t>
   </si>
   <si>
+    <t>55.1</t>
+  </si>
+  <si>
     <t>44.2</t>
   </si>
   <si>
     <t>67.0</t>
   </si>
   <si>
-    <t>55.1</t>
+    <t>126.8</t>
   </si>
   <si>
     <t>111.2</t>
   </si>
   <si>
-    <t>126.8</t>
-  </si>
-  <si>
     <t>143.8</t>
   </si>
   <si>
     <t>179.1</t>
   </si>
   <si>
+    <t>172.8</t>
+  </si>
+  <si>
     <t>165.9</t>
   </si>
   <si>
-    <t>172.8</t>
+    <t>217.7</t>
+  </si>
+  <si>
+    <t>209.8</t>
   </si>
   <si>
     <t>201.2</t>
   </si>
   <si>
-    <t>217.7</t>
-  </si>
-  <si>
-    <t>209.8</t>
-  </si>
-  <si>
     <t>75.1</t>
   </si>
   <si>
@@ -1114,10 +1114,13 @@
     <t>84.1</t>
   </si>
   <si>
+    <t>165.2</t>
+  </si>
+  <si>
     <t>130.9</t>
   </si>
   <si>
-    <t>165.2</t>
+    <t>171.5</t>
   </si>
   <si>
     <t>175.3</t>
@@ -1126,9 +1129,6 @@
     <t>173.5</t>
   </si>
   <si>
-    <t>171.5</t>
-  </si>
-  <si>
     <t>219.4</t>
   </si>
   <si>
@@ -1138,12 +1138,12 @@
     <t>199.9</t>
   </si>
   <si>
+    <t>83.1</t>
+  </si>
+  <si>
     <t>68.8</t>
   </si>
   <si>
-    <t>83.1</t>
-  </si>
-  <si>
     <t>75.6</t>
   </si>
   <si>
@@ -1165,13 +1165,16 @@
     <t>206.6</t>
   </si>
   <si>
+    <t>269.1</t>
+  </si>
+  <si>
     <t>257.9</t>
   </si>
   <si>
     <t>245.7</t>
   </si>
   <si>
-    <t>269.1</t>
+    <t>64.5</t>
   </si>
   <si>
     <t>91.1</t>
@@ -1180,7 +1183,7 @@
     <t>77.3</t>
   </si>
   <si>
-    <t>64.5</t>
+    <t>129.0</t>
   </si>
   <si>
     <t>186.7</t>
@@ -1189,27 +1192,24 @@
     <t>156.7</t>
   </si>
   <si>
-    <t>129.0</t>
+    <t>193.5</t>
+  </si>
+  <si>
+    <t>190.7</t>
   </si>
   <si>
     <t>196.0</t>
   </si>
   <si>
-    <t>193.5</t>
-  </si>
-  <si>
-    <t>190.7</t>
-  </si>
-  <si>
     <t>231.3</t>
   </si>
   <si>
+    <t>224.2</t>
+  </si>
+  <si>
     <t>237.8</t>
   </si>
   <si>
-    <t>224.2</t>
-  </si>
-  <si>
     <t>99.2</t>
   </si>
   <si>
@@ -1219,15 +1219,15 @@
     <t>109.5</t>
   </si>
   <si>
+    <t>146.6</t>
+  </si>
+  <si>
+    <t>188.5</t>
+  </si>
+  <si>
     <t>166.7</t>
   </si>
   <si>
-    <t>146.6</t>
-  </si>
-  <si>
-    <t>188.5</t>
-  </si>
-  <si>
     <t>189.5</t>
   </si>
   <si>
@@ -1240,70 +1240,73 @@
     <t>112.2</t>
   </si>
   <si>
+    <t>72.5</t>
+  </si>
+  <si>
     <t>91.6</t>
   </si>
   <si>
-    <t>72.5</t>
+    <t>146.4</t>
   </si>
   <si>
     <t>172.1</t>
   </si>
   <si>
-    <t>146.4</t>
+    <t>224.7</t>
+  </si>
+  <si>
+    <t>217.9</t>
   </si>
   <si>
     <t>221.2</t>
   </si>
   <si>
-    <t>224.7</t>
-  </si>
-  <si>
-    <t>217.9</t>
+    <t>270.5</t>
   </si>
   <si>
     <t>268.5</t>
   </si>
   <si>
-    <t>270.5</t>
-  </si>
-  <si>
     <t>269.6</t>
   </si>
   <si>
+    <t>110.6</t>
+  </si>
+  <si>
     <t>118.7</t>
   </si>
   <si>
     <t>103.2</t>
   </si>
   <si>
-    <t>110.6</t>
-  </si>
-  <si>
     <t>194.5</t>
   </si>
   <si>
+    <t>196.5</t>
+  </si>
+  <si>
     <t>203.5</t>
   </si>
   <si>
-    <t>196.5</t>
+    <t>248.0</t>
+  </si>
+  <si>
+    <t>248.3</t>
   </si>
   <si>
     <t>248.1</t>
   </si>
   <si>
-    <t>248.0</t>
-  </si>
-  <si>
-    <t>248.3</t>
+    <t>103.3</t>
+  </si>
+  <si>
+    <t>122.9</t>
   </si>
   <si>
     <t>85.3</t>
   </si>
   <si>
-    <t>122.9</t>
-  </si>
-  <si>
-    <t>103.3</t>
+    <t>194.2</t>
   </si>
   <si>
     <t>211.0</t>
@@ -1312,22 +1315,22 @@
     <t>178.7</t>
   </si>
   <si>
-    <t>194.2</t>
-  </si>
-  <si>
     <t>187.5</t>
   </si>
   <si>
     <t>179.2</t>
   </si>
   <si>
+    <t>244.9</t>
+  </si>
+  <si>
     <t>246.8</t>
   </si>
   <si>
     <t>243.2</t>
   </si>
   <si>
-    <t>244.9</t>
+    <t>71.2</t>
   </si>
   <si>
     <t>60.6</t>
@@ -1336,36 +1339,33 @@
     <t>82.7</t>
   </si>
   <si>
-    <t>71.2</t>
+    <t>165.5</t>
+  </si>
+  <si>
+    <t>151.2</t>
   </si>
   <si>
     <t>181.0</t>
   </si>
   <si>
-    <t>151.2</t>
-  </si>
-  <si>
-    <t>165.5</t>
+    <t>194.7</t>
+  </si>
+  <si>
+    <t>201.5</t>
   </si>
   <si>
     <t>209.0</t>
   </si>
   <si>
-    <t>194.7</t>
-  </si>
-  <si>
-    <t>201.5</t>
+    <t>272.0</t>
+  </si>
+  <si>
+    <t>283.6</t>
   </si>
   <si>
     <t>261.4</t>
   </si>
   <si>
-    <t>272.0</t>
-  </si>
-  <si>
-    <t>283.6</t>
-  </si>
-  <si>
     <t>99.7</t>
   </si>
   <si>
@@ -1375,13 +1375,16 @@
     <t>85.0</t>
   </si>
   <si>
+    <t>174.9</t>
+  </si>
+  <si>
+    <t>201.9</t>
+  </si>
+  <si>
     <t>231.1</t>
   </si>
   <si>
-    <t>174.9</t>
-  </si>
-  <si>
-    <t>201.9</t>
+    <t>221.0</t>
   </si>
   <si>
     <t>230.5</t>
@@ -1390,66 +1393,63 @@
     <t>212.3</t>
   </si>
   <si>
-    <t>221.0</t>
+    <t>284.4</t>
+  </si>
+  <si>
+    <t>276.9</t>
   </si>
   <si>
     <t>292.5</t>
   </si>
   <si>
-    <t>284.4</t>
-  </si>
-  <si>
-    <t>276.9</t>
-  </si>
-  <si>
     <t>71.4</t>
   </si>
   <si>
+    <t>104.2</t>
+  </si>
+  <si>
     <t>87.1</t>
   </si>
   <si>
-    <t>104.2</t>
+    <t>181.7</t>
   </si>
   <si>
     <t>199.8</t>
   </si>
   <si>
-    <t>181.7</t>
-  </si>
-  <si>
     <t>Adjusted rate</t>
   </si>
   <si>
+    <t>108.2</t>
+  </si>
+  <si>
     <t>95.2</t>
   </si>
   <si>
-    <t>108.2</t>
+    <t>158.4</t>
   </si>
   <si>
     <t>129.8</t>
   </si>
   <si>
-    <t>158.4</t>
+    <t>39.9</t>
   </si>
   <si>
     <t>26.8</t>
   </si>
   <si>
-    <t>39.9</t>
-  </si>
-  <si>
     <t>32.9</t>
   </si>
   <si>
+    <t>85.9</t>
+  </si>
+  <si>
+    <t>100.3</t>
+  </si>
+  <si>
     <t>73.5</t>
   </si>
   <si>
-    <t>100.3</t>
-  </si>
-  <si>
-    <t>85.9</t>
-  </si>
-  <si>
     <t>87.0</t>
   </si>
   <si>
@@ -1480,123 +1480,123 @@
     <t>50.7</t>
   </si>
   <si>
+    <t>73.1</t>
+  </si>
+  <si>
     <t>101.0</t>
   </si>
   <si>
-    <t>73.1</t>
-  </si>
-  <si>
     <t>114.6</t>
   </si>
   <si>
+    <t>97.5</t>
+  </si>
+  <si>
     <t>84.0</t>
   </si>
   <si>
-    <t>97.5</t>
+    <t>150.4</t>
+  </si>
+  <si>
+    <t>126.0</t>
   </si>
   <si>
     <t>137.9</t>
   </si>
   <si>
-    <t>150.4</t>
-  </si>
-  <si>
-    <t>126.0</t>
+    <t>53.3</t>
+  </si>
+  <si>
+    <t>46.5</t>
   </si>
   <si>
     <t>40.9</t>
   </si>
   <si>
-    <t>46.5</t>
-  </si>
-  <si>
-    <t>53.3</t>
+    <t>80.9</t>
+  </si>
+  <si>
+    <t>119.7</t>
   </si>
   <si>
     <t>98.4</t>
   </si>
   <si>
-    <t>80.9</t>
-  </si>
-  <si>
-    <t>119.7</t>
+    <t>115.8</t>
   </si>
   <si>
     <t>132.4</t>
   </si>
   <si>
-    <t>115.8</t>
+    <t>188.4</t>
   </si>
   <si>
     <t>165.8</t>
   </si>
   <si>
-    <t>188.4</t>
-  </si>
-  <si>
     <t>148.2</t>
   </si>
   <si>
+    <t>38.3</t>
+  </si>
+  <si>
     <t>27.9</t>
   </si>
   <si>
     <t>51.6</t>
   </si>
   <si>
-    <t>38.3</t>
+    <t>84.4</t>
   </si>
   <si>
     <t>64.1</t>
   </si>
   <si>
-    <t>84.4</t>
-  </si>
-  <si>
     <t>111.5</t>
   </si>
   <si>
     <t>106.6</t>
   </si>
   <si>
+    <t>115.3</t>
+  </si>
+  <si>
     <t>125.3</t>
   </si>
   <si>
-    <t>115.3</t>
+    <t>137.4</t>
   </si>
   <si>
     <t>151.7</t>
   </si>
   <si>
-    <t>137.4</t>
-  </si>
-  <si>
     <t>70.4</t>
   </si>
   <si>
     <t>72.3</t>
   </si>
   <si>
+    <t>126.4</t>
+  </si>
+  <si>
     <t>102.4</t>
   </si>
   <si>
     <t>113.8</t>
   </si>
   <si>
-    <t>126.4</t>
-  </si>
-  <si>
     <t>135.5</t>
   </si>
   <si>
     <t>147.4</t>
   </si>
   <si>
+    <t>63.1</t>
+  </si>
+  <si>
     <t>40.4</t>
   </si>
   <si>
-    <t>63.1</t>
-  </si>
-  <si>
     <t>51.2</t>
   </si>
   <si>
@@ -1615,39 +1615,39 @@
     <t>122.0</t>
   </si>
   <si>
+    <t>154.1</t>
+  </si>
+  <si>
     <t>178.1</t>
   </si>
   <si>
-    <t>154.1</t>
+    <t>38.0</t>
   </si>
   <si>
     <t>67.3</t>
   </si>
   <si>
-    <t>38.0</t>
+    <t>70.3</t>
   </si>
   <si>
     <t>136.1</t>
   </si>
   <si>
-    <t>70.3</t>
+    <t>137.2</t>
   </si>
   <si>
     <t>113.2</t>
   </si>
   <si>
-    <t>137.2</t>
-  </si>
-  <si>
     <t>146.3</t>
   </si>
   <si>
+    <t>161.0</t>
+  </si>
+  <si>
     <t>133.8</t>
   </si>
   <si>
-    <t>161.0</t>
-  </si>
-  <si>
     <t>64.3</t>
   </si>
   <si>
@@ -1657,15 +1657,15 @@
     <t>77.9</t>
   </si>
   <si>
+    <t>81.2</t>
+  </si>
+  <si>
+    <t>134.6</t>
+  </si>
+  <si>
     <t>104.9</t>
   </si>
   <si>
-    <t>81.2</t>
-  </si>
-  <si>
-    <t>134.6</t>
-  </si>
-  <si>
     <t>107.7</t>
   </si>
   <si>
@@ -1675,12 +1675,12 @@
     <t>124.2</t>
   </si>
   <si>
+    <t>170.3</t>
+  </si>
+  <si>
     <t>151.3</t>
   </si>
   <si>
-    <t>170.3</t>
-  </si>
-  <si>
     <t>134.1</t>
   </si>
   <si>
@@ -1690,40 +1690,43 @@
     <t>58.3</t>
   </si>
   <si>
+    <t>77.8</t>
+  </si>
+  <si>
+    <t>106.8</t>
+  </si>
+  <si>
     <t>142.3</t>
   </si>
   <si>
-    <t>106.8</t>
-  </si>
-  <si>
-    <t>77.8</t>
+    <t>152.2</t>
+  </si>
+  <si>
+    <t>119.1</t>
   </si>
   <si>
     <t>135.1</t>
   </si>
   <si>
-    <t>152.2</t>
-  </si>
-  <si>
-    <t>119.1</t>
+    <t>144.1</t>
   </si>
   <si>
     <t>183.1</t>
   </si>
   <si>
-    <t>144.1</t>
-  </si>
-  <si>
     <t>162.5</t>
   </si>
   <si>
+    <t>68.4</t>
+  </si>
+  <si>
     <t>82.5</t>
   </si>
   <si>
     <t>55.4</t>
   </si>
   <si>
-    <t>68.4</t>
+    <t>140.5</t>
   </si>
   <si>
     <t>118.1</t>
@@ -1732,43 +1735,43 @@
     <t>97.6</t>
   </si>
   <si>
-    <t>140.5</t>
+    <t>110.1</t>
   </si>
   <si>
     <t>124.3</t>
   </si>
   <si>
-    <t>110.1</t>
+    <t>169.3</t>
+  </si>
+  <si>
+    <t>136.2</t>
   </si>
   <si>
     <t>152.3</t>
   </si>
   <si>
-    <t>169.3</t>
-  </si>
-  <si>
-    <t>136.2</t>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>84.7</t>
   </si>
   <si>
     <t>45.5</t>
   </si>
   <si>
-    <t>84.7</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
     <t>116.8</t>
   </si>
   <si>
+    <t>113.6</t>
+  </si>
+  <si>
+    <t>98.0</t>
+  </si>
+  <si>
     <t>133.0</t>
   </si>
   <si>
-    <t>113.6</t>
-  </si>
-  <si>
-    <t>98.0</t>
+    <t>144.7</t>
   </si>
   <si>
     <t>166.9</t>
@@ -1777,7 +1780,7 @@
     <t>126.9</t>
   </si>
   <si>
-    <t>144.7</t>
+    <t>44.8</t>
   </si>
   <si>
     <t>34.0</t>
@@ -1786,33 +1789,30 @@
     <t>57.2</t>
   </si>
   <si>
-    <t>44.8</t>
+    <t>97.3</t>
   </si>
   <si>
     <t>76.5</t>
   </si>
   <si>
-    <t>97.3</t>
+    <t>106.2</t>
+  </si>
+  <si>
+    <t>119.6</t>
   </si>
   <si>
     <t>135.6</t>
   </si>
   <si>
-    <t>106.2</t>
-  </si>
-  <si>
-    <t>119.6</t>
+    <t>158.7</t>
+  </si>
+  <si>
+    <t>187.1</t>
   </si>
   <si>
     <t>136.0</t>
   </si>
   <si>
-    <t>158.7</t>
-  </si>
-  <si>
-    <t>187.1</t>
-  </si>
-  <si>
     <t>65.5</t>
   </si>
   <si>
@@ -1822,13 +1822,16 @@
     <t>50.9</t>
   </si>
   <si>
+    <t>87.9</t>
+  </si>
+  <si>
+    <t>116.5</t>
+  </si>
+  <si>
     <t>153.9</t>
   </si>
   <si>
-    <t>87.9</t>
-  </si>
-  <si>
-    <t>116.5</t>
+    <t>130.4</t>
   </si>
   <si>
     <t>154.0</t>
@@ -1837,25 +1840,25 @@
     <t>111.9</t>
   </si>
   <si>
-    <t>130.4</t>
+    <t>166.5</t>
+  </si>
+  <si>
+    <t>141.0</t>
   </si>
   <si>
     <t>197.9</t>
   </si>
   <si>
-    <t>166.5</t>
-  </si>
-  <si>
-    <t>141.0</t>
-  </si>
-  <si>
     <t>38.4</t>
   </si>
   <si>
+    <t>68.0</t>
+  </si>
+  <si>
     <t>52.3</t>
   </si>
   <si>
-    <t>68.0</t>
+    <t>89.9</t>
   </si>
   <si>
     <t>115.6</t>
@@ -1864,42 +1867,39 @@
     <t>144.8</t>
   </si>
   <si>
-    <t>89.9</t>
-  </si>
-  <si>
     <t>Lower 95% limit</t>
   </si>
   <si>
+    <t>98.1</t>
+  </si>
+  <si>
     <t>82.8</t>
   </si>
   <si>
-    <t>98.1</t>
+    <t>139.6</t>
   </si>
   <si>
     <t>132.1</t>
   </si>
   <si>
-    <t>139.6</t>
+    <t>30.8</t>
   </si>
   <si>
     <t>20.2</t>
   </si>
   <si>
-    <t>30.8</t>
-  </si>
-  <si>
     <t>27.3</t>
   </si>
   <si>
+    <t>76.9</t>
+  </si>
+  <si>
+    <t>85.5</t>
+  </si>
+  <si>
     <t>62.8</t>
   </si>
   <si>
-    <t>85.5</t>
-  </si>
-  <si>
-    <t>76.9</t>
-  </si>
-  <si>
     <t>75.0</t>
   </si>
   <si>
@@ -1930,93 +1930,93 @@
     <t>42.0</t>
   </si>
   <si>
+    <t>64.8</t>
+  </si>
+  <si>
     <t>86.2</t>
   </si>
   <si>
-    <t>64.8</t>
-  </si>
-  <si>
     <t>99.0</t>
   </si>
   <si>
     <t>88.0</t>
   </si>
   <si>
+    <t>132.5</t>
+  </si>
+  <si>
     <t>126.7</t>
   </si>
   <si>
-    <t>132.5</t>
+    <t>42.8</t>
   </si>
   <si>
     <t>40.0</t>
   </si>
   <si>
-    <t>42.8</t>
+    <t>69.7</t>
+  </si>
+  <si>
+    <t>103.7</t>
   </si>
   <si>
     <t>88.9</t>
   </si>
   <si>
-    <t>69.7</t>
-  </si>
-  <si>
-    <t>103.7</t>
+    <t>135.3</t>
+  </si>
+  <si>
+    <t>102.3</t>
   </si>
   <si>
     <t>121.4</t>
   </si>
   <si>
-    <t>135.3</t>
-  </si>
-  <si>
-    <t>102.3</t>
+    <t>168.4</t>
   </si>
   <si>
     <t>153.5</t>
   </si>
   <si>
-    <t>168.4</t>
-  </si>
-  <si>
     <t>132.9</t>
   </si>
   <si>
+    <t>32.4</t>
+  </si>
+  <si>
     <t>21.3</t>
   </si>
   <si>
     <t>41.4</t>
   </si>
   <si>
-    <t>32.4</t>
+    <t>75.7</t>
   </si>
   <si>
     <t>54.3</t>
   </si>
   <si>
-    <t>75.7</t>
-  </si>
-  <si>
     <t>96.2</t>
   </si>
   <si>
     <t>93.6</t>
   </si>
   <si>
+    <t>105.0</t>
+  </si>
+  <si>
     <t>109.2</t>
   </si>
   <si>
-    <t>105.0</t>
+    <t>112.4</t>
+  </si>
+  <si>
+    <t>126.3</t>
   </si>
   <si>
     <t>134.0</t>
   </si>
   <si>
-    <t>112.4</t>
-  </si>
-  <si>
-    <t>126.3</t>
-  </si>
-  <si>
     <t>36.3</t>
   </si>
   <si>
@@ -2029,18 +2029,18 @@
     <t>86.1</t>
   </si>
   <si>
+    <t>108.1</t>
+  </si>
+  <si>
     <t>62.1</t>
   </si>
   <si>
-    <t>108.1</t>
+    <t>110.5</t>
   </si>
   <si>
     <t>103.8</t>
   </si>
   <si>
-    <t>110.5</t>
-  </si>
-  <si>
     <t>110.3</t>
   </si>
   <si>
@@ -2050,12 +2050,12 @@
     <t>130.1</t>
   </si>
   <si>
+    <t>51.8</t>
+  </si>
+  <si>
     <t>32.7</t>
   </si>
   <si>
-    <t>51.8</t>
-  </si>
-  <si>
     <t>81.3</t>
   </si>
   <si>
@@ -2065,36 +2065,36 @@
     <t>120.8</t>
   </si>
   <si>
+    <t>138.5</t>
+  </si>
+  <si>
     <t>153.7</t>
   </si>
   <si>
     <t>159.3</t>
   </si>
   <si>
-    <t>138.5</t>
+    <t>30.5</t>
   </si>
   <si>
     <t>55.8</t>
   </si>
   <si>
-    <t>30.5</t>
+    <t>60.3</t>
   </si>
   <si>
     <t>91.0</t>
   </si>
   <si>
-    <t>60.3</t>
-  </si>
-  <si>
     <t>100.0</t>
   </si>
   <si>
+    <t>143.2</t>
+  </si>
+  <si>
     <t>119.5</t>
   </si>
   <si>
-    <t>143.2</t>
-  </si>
-  <si>
     <t>56.8</t>
   </si>
   <si>
@@ -2104,12 +2104,12 @@
     <t>65.7</t>
   </si>
   <si>
+    <t>118.4</t>
+  </si>
+  <si>
     <t>95.5</t>
   </si>
   <si>
-    <t>118.4</t>
-  </si>
-  <si>
     <t>94.8</t>
   </si>
   <si>
@@ -2125,12 +2125,12 @@
     <t>33.3</t>
   </si>
   <si>
+    <t>97.4</t>
+  </si>
+  <si>
     <t>125.6</t>
   </si>
   <si>
-    <t>97.4</t>
-  </si>
-  <si>
     <t>135.4</t>
   </si>
   <si>
@@ -2143,40 +2143,43 @@
     <t>151.0</t>
   </si>
   <si>
+    <t>60.8</t>
+  </si>
+  <si>
     <t>70.0</t>
   </si>
   <si>
     <t>46.7</t>
   </si>
   <si>
-    <t>60.8</t>
-  </si>
-  <si>
     <t>124.1</t>
   </si>
   <si>
+    <t>97.2</t>
+  </si>
+  <si>
+    <t>114.0</t>
+  </si>
+  <si>
     <t>123.1</t>
   </si>
   <si>
-    <t>114.0</t>
-  </si>
-  <si>
-    <t>97.2</t>
+    <t>151.4</t>
+  </si>
+  <si>
+    <t>121.9</t>
   </si>
   <si>
     <t>140.9</t>
   </si>
   <si>
-    <t>151.4</t>
-  </si>
-  <si>
-    <t>121.9</t>
+    <t>72.2</t>
   </si>
   <si>
     <t>37.7</t>
   </si>
   <si>
-    <t>72.2</t>
+    <t>107.0</t>
   </si>
   <si>
     <t>129.9</t>
@@ -2185,22 +2188,22 @@
     <t>80.1</t>
   </si>
   <si>
-    <t>107.0</t>
+    <t>103.9</t>
+  </si>
+  <si>
+    <t>86.0</t>
   </si>
   <si>
     <t>117.3</t>
   </si>
   <si>
-    <t>103.9</t>
-  </si>
-  <si>
-    <t>86.0</t>
+    <t>133.9</t>
   </si>
   <si>
     <t>149.2</t>
   </si>
   <si>
-    <t>133.9</t>
+    <t>38.6</t>
   </si>
   <si>
     <t>27.0</t>
@@ -2209,60 +2212,57 @@
     <t>46.9</t>
   </si>
   <si>
-    <t>38.6</t>
-  </si>
-  <si>
     <t>88.5</t>
   </si>
   <si>
+    <t>109.7</t>
+  </si>
+  <si>
     <t>120.0</t>
   </si>
   <si>
-    <t>109.7</t>
+    <t>168.6</t>
   </si>
   <si>
     <t>122.1</t>
   </si>
   <si>
-    <t>168.6</t>
-  </si>
-  <si>
     <t>54.7</t>
   </si>
   <si>
     <t>44.5</t>
   </si>
   <si>
+    <t>77.2</t>
+  </si>
+  <si>
+    <t>106.9</t>
+  </si>
+  <si>
     <t>137.1</t>
   </si>
   <si>
-    <t>77.2</t>
-  </si>
-  <si>
-    <t>106.9</t>
+    <t>154.8</t>
   </si>
   <si>
     <t>178.4</t>
   </si>
   <si>
-    <t>154.8</t>
-  </si>
-  <si>
     <t>31.1</t>
   </si>
   <si>
     <t>57.0</t>
   </si>
   <si>
+    <t>79.0</t>
+  </si>
+  <si>
     <t>106.0</t>
   </si>
   <si>
     <t>128.5</t>
   </si>
   <si>
-    <t>79.0</t>
-  </si>
-  <si>
     <t>Upper 95% limit</t>
   </si>
   <si>
@@ -2284,15 +2284,15 @@
     <t>39.3</t>
   </si>
   <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>117.0</t>
+  </si>
+  <si>
     <t>85.8</t>
   </si>
   <si>
-    <t>117.0</t>
-  </si>
-  <si>
-    <t>95.8</t>
-  </si>
-  <si>
     <t>100.5</t>
   </si>
   <si>
@@ -2317,63 +2317,63 @@
     <t>61.1</t>
   </si>
   <si>
+    <t>82.2</t>
+  </si>
+  <si>
     <t>117.7</t>
   </si>
   <si>
-    <t>82.2</t>
+    <t>107.8</t>
   </si>
   <si>
     <t>97.0</t>
   </si>
   <si>
-    <t>107.8</t>
+    <t>170.2</t>
   </si>
   <si>
     <t>149.9</t>
   </si>
   <si>
-    <t>170.2</t>
+    <t>65.6</t>
   </si>
   <si>
     <t>53.9</t>
   </si>
   <si>
-    <t>65.6</t>
+    <t>93.5</t>
+  </si>
+  <si>
+    <t>137.6</t>
   </si>
   <si>
     <t>108.7</t>
   </si>
   <si>
-    <t>93.5</t>
-  </si>
-  <si>
-    <t>137.6</t>
+    <t>173.2</t>
   </si>
   <si>
     <t>144.3</t>
   </si>
   <si>
-    <t>173.2</t>
+    <t>210.2</t>
   </si>
   <si>
     <t>178.9</t>
   </si>
   <si>
-    <t>210.2</t>
-  </si>
-  <si>
     <t>164.9</t>
   </si>
   <si>
+    <t>45.1</t>
+  </si>
+  <si>
     <t>36.1</t>
   </si>
   <si>
     <t>63.8</t>
   </si>
   <si>
-    <t>45.1</t>
-  </si>
-  <si>
     <t>75.4</t>
   </si>
   <si>
@@ -2386,15 +2386,15 @@
     <t>143.3</t>
   </si>
   <si>
+    <t>142.1</t>
+  </si>
+  <si>
+    <t>149.4</t>
+  </si>
+  <si>
     <t>171.3</t>
   </si>
   <si>
-    <t>142.1</t>
-  </si>
-  <si>
-    <t>149.4</t>
-  </si>
-  <si>
     <t>54.1</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>141.8</t>
   </si>
   <si>
+    <t>144.2</t>
+  </si>
+  <si>
     <t>116.6</t>
   </si>
   <si>
     <t>124.7</t>
   </si>
   <si>
-    <t>144.2</t>
-  </si>
-  <si>
     <t>139.2</t>
   </si>
   <si>
@@ -2425,12 +2425,12 @@
     <t>166.4</t>
   </si>
   <si>
+    <t>76.3</t>
+  </si>
+  <si>
     <t>49.7</t>
   </si>
   <si>
-    <t>76.3</t>
-  </si>
-  <si>
     <t>58.8</t>
   </si>
   <si>
@@ -2443,10 +2443,13 @@
     <t>159.7</t>
   </si>
   <si>
+    <t>171.2</t>
+  </si>
+  <si>
     <t>198.8</t>
   </si>
   <si>
-    <t>171.2</t>
+    <t>47.1</t>
   </si>
   <si>
     <t>80.7</t>
@@ -2455,84 +2458,81 @@
     <t>59.2</t>
   </si>
   <si>
-    <t>47.1</t>
-  </si>
-  <si>
     <t>81.8</t>
   </si>
   <si>
+    <t>135.2</t>
+  </si>
+  <si>
+    <t>155.5</t>
+  </si>
+  <si>
     <t>127.9</t>
   </si>
   <si>
-    <t>135.2</t>
-  </si>
-  <si>
-    <t>155.5</t>
+    <t>180.6</t>
   </si>
   <si>
     <t>149.6</t>
   </si>
   <si>
-    <t>180.6</t>
-  </si>
-  <si>
     <t>63.2</t>
   </si>
   <si>
     <t>91.9</t>
   </si>
   <si>
+    <t>152.6</t>
+  </si>
+  <si>
     <t>115.2</t>
   </si>
   <si>
-    <t>152.6</t>
-  </si>
-  <si>
     <t>161.5</t>
   </si>
   <si>
+    <t>190.4</t>
+  </si>
+  <si>
     <t>163.6</t>
   </si>
   <si>
-    <t>190.4</t>
-  </si>
-  <si>
     <t>149.8</t>
   </si>
   <si>
     <t>94.1</t>
   </si>
   <si>
+    <t>50.0</t>
+  </si>
+  <si>
     <t>66.1</t>
   </si>
   <si>
-    <t>50.0</t>
+    <t>89.6</t>
+  </si>
+  <si>
+    <t>117.1</t>
   </si>
   <si>
     <t>160.7</t>
   </si>
   <si>
-    <t>117.1</t>
-  </si>
-  <si>
-    <t>89.6</t>
+    <t>170.8</t>
+  </si>
+  <si>
+    <t>133.7</t>
   </si>
   <si>
     <t>146.5</t>
   </si>
   <si>
-    <t>170.8</t>
-  </si>
-  <si>
-    <t>133.7</t>
+    <t>159.9</t>
   </si>
   <si>
     <t>203.4</t>
   </si>
   <si>
-    <t>159.9</t>
-  </si>
-  <si>
     <t>174.8</t>
   </si>
   <si>
@@ -2545,31 +2545,34 @@
     <t>157.4</t>
   </si>
   <si>
+    <t>189.0</t>
+  </si>
+  <si>
+    <t>152.1</t>
+  </si>
+  <si>
     <t>164.5</t>
   </si>
   <si>
-    <t>189.0</t>
-  </si>
-  <si>
-    <t>152.1</t>
+    <t>70.9</t>
+  </si>
+  <si>
+    <t>99.1</t>
   </si>
   <si>
     <t>54.9</t>
   </si>
   <si>
-    <t>99.1</t>
-  </si>
-  <si>
-    <t>70.9</t>
-  </si>
-  <si>
     <t>150.6</t>
   </si>
   <si>
+    <t>156.3</t>
+  </si>
+  <si>
     <t>186.3</t>
   </si>
   <si>
-    <t>156.3</t>
+    <t>51.7</t>
   </si>
   <si>
     <t>42.6</t>
@@ -2578,21 +2581,18 @@
     <t>69.2</t>
   </si>
   <si>
-    <t>51.7</t>
-  </si>
-  <si>
     <t>138.7</t>
   </si>
   <si>
+    <t>120.2</t>
+  </si>
+  <si>
+    <t>130.2</t>
+  </si>
+  <si>
     <t>152.9</t>
   </si>
   <si>
-    <t>120.2</t>
-  </si>
-  <si>
-    <t>130.2</t>
-  </si>
-  <si>
     <t>207.4</t>
   </si>
   <si>
@@ -2605,10 +2605,13 @@
     <t>58.1</t>
   </si>
   <si>
+    <t>100.2</t>
+  </si>
+  <si>
     <t>172.6</t>
   </si>
   <si>
-    <t>100.2</t>
+    <t>141.5</t>
   </si>
   <si>
     <t>172.7</t>
@@ -2617,13 +2620,10 @@
     <t>126.1</t>
   </si>
   <si>
-    <t>141.5</t>
+    <t>156.5</t>
   </si>
   <si>
     <t>219.0</t>
-  </si>
-  <si>
-    <t>156.5</t>
   </si>
   <si>
     <t>47.3</t>
@@ -7562,7 +7562,7 @@
         <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D2" t="s">
         <v>307</v>
@@ -7571,13 +7571,13 @@
         <v>310</v>
       </c>
       <c r="F2" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
       <c r="G2" t="s">
-        <v>616</v>
+        <v>329</v>
       </c>
       <c r="H2" t="s">
-        <v>660</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3">
@@ -7588,7 +7588,7 @@
         <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
         <v>307</v>
@@ -7597,13 +7597,13 @@
         <v>311</v>
       </c>
       <c r="F3" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="G3" t="s">
-        <v>330</v>
+        <v>616</v>
       </c>
       <c r="H3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4">
@@ -7614,7 +7614,7 @@
         <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D4" t="s">
         <v>307</v>
@@ -7629,7 +7629,7 @@
         <v>617</v>
       </c>
       <c r="H4" t="s">
-        <v>749</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5">
@@ -7640,7 +7640,7 @@
         <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D5" t="s">
         <v>308</v>
@@ -7649,13 +7649,13 @@
         <v>313</v>
       </c>
       <c r="F5" t="s">
-        <v>354</v>
+        <v>468</v>
       </c>
       <c r="G5" t="s">
         <v>618</v>
       </c>
       <c r="H5" t="s">
-        <v>750</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6">
@@ -7666,7 +7666,7 @@
         <v>172</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D6" t="s">
         <v>308</v>
@@ -7675,13 +7675,13 @@
         <v>314</v>
       </c>
       <c r="F6" t="s">
-        <v>468</v>
+        <v>354</v>
       </c>
       <c r="G6" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="H6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -7692,7 +7692,7 @@
         <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D7" t="s">
         <v>308</v>
@@ -7704,10 +7704,10 @@
         <v>469</v>
       </c>
       <c r="G7" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="H7" t="s">
-        <v>355</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -7718,7 +7718,7 @@
         <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
         <v>307</v>
@@ -7733,7 +7733,7 @@
         <v>620</v>
       </c>
       <c r="H8" t="s">
-        <v>752</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9">
@@ -7744,7 +7744,7 @@
         <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D9" t="s">
         <v>307</v>
@@ -7759,7 +7759,7 @@
         <v>621</v>
       </c>
       <c r="H9" t="s">
-        <v>599</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10">
@@ -7796,7 +7796,7 @@
         <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
         <v>308</v>
@@ -7848,7 +7848,7 @@
         <v>220</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D13" t="s">
         <v>308</v>
@@ -7984,7 +7984,7 @@
         <v>308</v>
       </c>
       <c r="E18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F18" t="s">
         <v>480</v>
@@ -8134,7 +8134,7 @@
         <v>220</v>
       </c>
       <c r="C24" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D24" t="s">
         <v>308</v>
@@ -8160,7 +8160,7 @@
         <v>220</v>
       </c>
       <c r="C25" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D25" t="s">
         <v>308</v>
@@ -8201,7 +8201,7 @@
         <v>638</v>
       </c>
       <c r="H26" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27">
@@ -8212,7 +8212,7 @@
         <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D27" t="s">
         <v>307</v>
@@ -8224,7 +8224,7 @@
         <v>489</v>
       </c>
       <c r="G27" t="s">
-        <v>407</v>
+        <v>639</v>
       </c>
       <c r="H27" t="s">
         <v>767</v>
@@ -8238,7 +8238,7 @@
         <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D28" t="s">
         <v>307</v>
@@ -8250,7 +8250,7 @@
         <v>490</v>
       </c>
       <c r="G28" t="s">
-        <v>639</v>
+        <v>406</v>
       </c>
       <c r="H28" t="s">
         <v>768</v>
@@ -8264,7 +8264,7 @@
         <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D29" t="s">
         <v>308</v>
@@ -8290,7 +8290,7 @@
         <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D30" t="s">
         <v>308</v>
@@ -8302,10 +8302,10 @@
         <v>492</v>
       </c>
       <c r="G30" t="s">
-        <v>641</v>
+        <v>405</v>
       </c>
       <c r="H30" t="s">
-        <v>770</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31">
@@ -8316,7 +8316,7 @@
         <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D31" t="s">
         <v>308</v>
@@ -8328,10 +8328,10 @@
         <v>493</v>
       </c>
       <c r="G31" t="s">
-        <v>405</v>
+        <v>641</v>
       </c>
       <c r="H31" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
     </row>
     <row r="32">
@@ -8342,7 +8342,7 @@
         <v>220</v>
       </c>
       <c r="C32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D32" t="s">
         <v>307</v>
@@ -8354,10 +8354,10 @@
         <v>494</v>
       </c>
       <c r="G32" t="s">
-        <v>472</v>
+        <v>642</v>
       </c>
       <c r="H32" t="s">
-        <v>302</v>
+        <v>771</v>
       </c>
     </row>
     <row r="33">
@@ -8380,10 +8380,10 @@
         <v>495</v>
       </c>
       <c r="G33" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H33" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="34">
@@ -8394,7 +8394,7 @@
         <v>220</v>
       </c>
       <c r="C34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D34" t="s">
         <v>307</v>
@@ -8406,10 +8406,10 @@
         <v>496</v>
       </c>
       <c r="G34" t="s">
-        <v>643</v>
+        <v>472</v>
       </c>
       <c r="H34" t="s">
-        <v>772</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35">
@@ -8420,7 +8420,7 @@
         <v>220</v>
       </c>
       <c r="C35" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D35" t="s">
         <v>308</v>
@@ -8446,7 +8446,7 @@
         <v>220</v>
       </c>
       <c r="C36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s">
         <v>308</v>
@@ -8472,7 +8472,7 @@
         <v>220</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D37" t="s">
         <v>308</v>
@@ -8498,7 +8498,7 @@
         <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D38" t="s">
         <v>307</v>
@@ -8507,7 +8507,7 @@
         <v>343</v>
       </c>
       <c r="F38" t="s">
-        <v>500</v>
+        <v>341</v>
       </c>
       <c r="G38" t="s">
         <v>647</v>
@@ -8524,7 +8524,7 @@
         <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D39" t="s">
         <v>307</v>
@@ -8533,13 +8533,13 @@
         <v>344</v>
       </c>
       <c r="F39" t="s">
-        <v>342</v>
+        <v>500</v>
       </c>
       <c r="G39" t="s">
         <v>648</v>
       </c>
       <c r="H39" t="s">
-        <v>777</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40">
@@ -8550,7 +8550,7 @@
         <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s">
         <v>307</v>
@@ -8565,7 +8565,7 @@
         <v>649</v>
       </c>
       <c r="H40" t="s">
-        <v>364</v>
+        <v>777</v>
       </c>
     </row>
     <row r="41">
@@ -8576,7 +8576,7 @@
         <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D41" t="s">
         <v>308</v>
@@ -8602,7 +8602,7 @@
         <v>172</v>
       </c>
       <c r="C42" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D42" t="s">
         <v>308</v>
@@ -8654,7 +8654,7 @@
         <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D44" t="s">
         <v>307</v>
@@ -8680,7 +8680,7 @@
         <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -8706,7 +8706,7 @@
         <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D46" t="s">
         <v>307</v>
@@ -8732,7 +8732,7 @@
         <v>220</v>
       </c>
       <c r="C47" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D47" t="s">
         <v>308</v>
@@ -8747,7 +8747,7 @@
         <v>656</v>
       </c>
       <c r="H47" t="s">
-        <v>784</v>
+        <v>628</v>
       </c>
     </row>
     <row r="48">
@@ -8758,7 +8758,7 @@
         <v>220</v>
       </c>
       <c r="C48" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D48" t="s">
         <v>308</v>
@@ -8773,7 +8773,7 @@
         <v>657</v>
       </c>
       <c r="H48" t="s">
-        <v>628</v>
+        <v>784</v>
       </c>
     </row>
     <row r="49">
@@ -8836,7 +8836,7 @@
         <v>172</v>
       </c>
       <c r="C51" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D51" t="s">
         <v>307</v>
@@ -8851,7 +8851,7 @@
         <v>660</v>
       </c>
       <c r="H51" t="s">
-        <v>787</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52">
@@ -8862,7 +8862,7 @@
         <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D52" t="s">
         <v>307</v>
@@ -8877,7 +8877,7 @@
         <v>661</v>
       </c>
       <c r="H52" t="s">
-        <v>520</v>
+        <v>787</v>
       </c>
     </row>
     <row r="53">
@@ -8888,7 +8888,7 @@
         <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D53" t="s">
         <v>308</v>
@@ -8897,7 +8897,7 @@
         <v>358</v>
       </c>
       <c r="F53" t="s">
-        <v>514</v>
+        <v>376</v>
       </c>
       <c r="G53" t="s">
         <v>662</v>
@@ -8914,7 +8914,7 @@
         <v>172</v>
       </c>
       <c r="C54" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D54" t="s">
         <v>308</v>
@@ -8923,7 +8923,7 @@
         <v>359</v>
       </c>
       <c r="F54" t="s">
-        <v>376</v>
+        <v>514</v>
       </c>
       <c r="G54" t="s">
         <v>663</v>
@@ -8940,7 +8940,7 @@
         <v>172</v>
       </c>
       <c r="C55" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D55" t="s">
         <v>308</v>
@@ -9053,7 +9053,7 @@
         <v>331</v>
       </c>
       <c r="F59" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G59" t="s">
         <v>668</v>
@@ -9070,7 +9070,7 @@
         <v>220</v>
       </c>
       <c r="C60" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D60" t="s">
         <v>308</v>
@@ -9079,13 +9079,13 @@
         <v>364</v>
       </c>
       <c r="F60" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="G60" t="s">
         <v>669</v>
       </c>
       <c r="H60" t="s">
-        <v>489</v>
+        <v>794</v>
       </c>
     </row>
     <row r="61">
@@ -9096,7 +9096,7 @@
         <v>220</v>
       </c>
       <c r="C61" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D61" t="s">
         <v>308</v>
@@ -9105,13 +9105,13 @@
         <v>365</v>
       </c>
       <c r="F61" t="s">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="G61" t="s">
         <v>670</v>
       </c>
       <c r="H61" t="s">
-        <v>794</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62">
@@ -9122,7 +9122,7 @@
         <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D62" t="s">
         <v>307</v>
@@ -9134,7 +9134,7 @@
         <v>518</v>
       </c>
       <c r="G62" t="s">
-        <v>397</v>
+        <v>671</v>
       </c>
       <c r="H62" t="s">
         <v>795</v>
@@ -9148,7 +9148,7 @@
         <v>172</v>
       </c>
       <c r="C63" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D63" t="s">
         <v>307</v>
@@ -9160,7 +9160,7 @@
         <v>519</v>
       </c>
       <c r="G63" t="s">
-        <v>671</v>
+        <v>397</v>
       </c>
       <c r="H63" t="s">
         <v>796</v>
@@ -9174,7 +9174,7 @@
         <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D64" t="s">
         <v>307</v>
@@ -9278,7 +9278,7 @@
         <v>220</v>
       </c>
       <c r="C68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D68" t="s">
         <v>307</v>
@@ -9304,7 +9304,7 @@
         <v>220</v>
       </c>
       <c r="C69" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D69" t="s">
         <v>307</v>
@@ -9368,7 +9368,7 @@
         <v>526</v>
       </c>
       <c r="G71" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H71" t="s">
         <v>804</v>
@@ -9417,7 +9417,7 @@
         <v>377</v>
       </c>
       <c r="F73" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G73" t="s">
         <v>679</v>
@@ -9449,7 +9449,7 @@
         <v>680</v>
       </c>
       <c r="H74" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75">
@@ -9472,7 +9472,7 @@
         <v>529</v>
       </c>
       <c r="G75" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H75" t="s">
         <v>806</v>
@@ -9501,7 +9501,7 @@
         <v>377</v>
       </c>
       <c r="H76" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="77">
@@ -9512,7 +9512,7 @@
         <v>172</v>
       </c>
       <c r="C77" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D77" t="s">
         <v>308</v>
@@ -9521,13 +9521,13 @@
         <v>381</v>
       </c>
       <c r="F77" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="G77" t="s">
         <v>681</v>
       </c>
       <c r="H77" t="s">
-        <v>429</v>
+        <v>807</v>
       </c>
     </row>
     <row r="78">
@@ -9538,7 +9538,7 @@
         <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D78" t="s">
         <v>308</v>
@@ -9547,13 +9547,13 @@
         <v>382</v>
       </c>
       <c r="F78" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="G78" t="s">
         <v>682</v>
       </c>
       <c r="H78" t="s">
-        <v>807</v>
+        <v>430</v>
       </c>
     </row>
     <row r="79">
@@ -9564,7 +9564,7 @@
         <v>172</v>
       </c>
       <c r="C79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D79" t="s">
         <v>308</v>
@@ -9590,7 +9590,7 @@
         <v>220</v>
       </c>
       <c r="C80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D80" t="s">
         <v>307</v>
@@ -9616,7 +9616,7 @@
         <v>220</v>
       </c>
       <c r="C81" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D81" t="s">
         <v>307</v>
@@ -9625,10 +9625,10 @@
         <v>385</v>
       </c>
       <c r="F81" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="G81" t="s">
-        <v>588</v>
+        <v>685</v>
       </c>
       <c r="H81" t="s">
         <v>810</v>
@@ -9642,7 +9642,7 @@
         <v>220</v>
       </c>
       <c r="C82" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D82" t="s">
         <v>307</v>
@@ -9651,10 +9651,10 @@
         <v>386</v>
       </c>
       <c r="F82" t="s">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="G82" t="s">
-        <v>685</v>
+        <v>586</v>
       </c>
       <c r="H82" t="s">
         <v>811</v>
@@ -9668,7 +9668,7 @@
         <v>220</v>
       </c>
       <c r="C83" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D83" t="s">
         <v>308</v>
@@ -9680,10 +9680,10 @@
         <v>535</v>
       </c>
       <c r="G83" t="s">
-        <v>593</v>
+        <v>686</v>
       </c>
       <c r="H83" t="s">
-        <v>311</v>
+        <v>812</v>
       </c>
     </row>
     <row r="84">
@@ -9694,7 +9694,7 @@
         <v>220</v>
       </c>
       <c r="C84" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D84" t="s">
         <v>308</v>
@@ -9703,13 +9703,13 @@
         <v>388</v>
       </c>
       <c r="F84" t="s">
-        <v>474</v>
+        <v>536</v>
       </c>
       <c r="G84" t="s">
-        <v>686</v>
+        <v>592</v>
       </c>
       <c r="H84" t="s">
-        <v>672</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85">
@@ -9720,7 +9720,7 @@
         <v>220</v>
       </c>
       <c r="C85" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D85" t="s">
         <v>308</v>
@@ -9729,13 +9729,13 @@
         <v>389</v>
       </c>
       <c r="F85" t="s">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="G85" t="s">
         <v>687</v>
       </c>
       <c r="H85" t="s">
-        <v>812</v>
+        <v>671</v>
       </c>
     </row>
     <row r="86">
@@ -9746,7 +9746,7 @@
         <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D86" t="s">
         <v>307</v>
@@ -9755,10 +9755,10 @@
         <v>390</v>
       </c>
       <c r="F86" t="s">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="G86" t="s">
-        <v>688</v>
+        <v>580</v>
       </c>
       <c r="H86" t="s">
         <v>813</v>
@@ -9772,7 +9772,7 @@
         <v>172</v>
       </c>
       <c r="C87" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D87" t="s">
         <v>307</v>
@@ -9781,10 +9781,10 @@
         <v>391</v>
       </c>
       <c r="F87" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="G87" t="s">
-        <v>581</v>
+        <v>680</v>
       </c>
       <c r="H87" t="s">
         <v>814</v>
@@ -9798,7 +9798,7 @@
         <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D88" t="s">
         <v>307</v>
@@ -9810,7 +9810,7 @@
         <v>538</v>
       </c>
       <c r="G88" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="H88" t="s">
         <v>815</v>
@@ -9836,10 +9836,10 @@
         <v>539</v>
       </c>
       <c r="G89" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H89" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90">
@@ -9850,7 +9850,7 @@
         <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D90" t="s">
         <v>308</v>
@@ -9876,7 +9876,7 @@
         <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D91" t="s">
         <v>308</v>
@@ -9917,7 +9917,7 @@
         <v>691</v>
       </c>
       <c r="H92" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="93">
@@ -9980,7 +9980,7 @@
         <v>220</v>
       </c>
       <c r="C95" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D95" t="s">
         <v>308</v>
@@ -9992,10 +9992,10 @@
         <v>545</v>
       </c>
       <c r="G95" t="s">
-        <v>694</v>
+        <v>535</v>
       </c>
       <c r="H95" t="s">
-        <v>820</v>
+        <v>773</v>
       </c>
     </row>
     <row r="96">
@@ -10006,7 +10006,7 @@
         <v>220</v>
       </c>
       <c r="C96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D96" t="s">
         <v>308</v>
@@ -10018,10 +10018,10 @@
         <v>546</v>
       </c>
       <c r="G96" t="s">
-        <v>536</v>
+        <v>694</v>
       </c>
       <c r="H96" t="s">
-        <v>774</v>
+        <v>820</v>
       </c>
     </row>
     <row r="97">
@@ -10032,7 +10032,7 @@
         <v>220</v>
       </c>
       <c r="C97" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D97" t="s">
         <v>308</v>
@@ -10096,7 +10096,7 @@
         <v>549</v>
       </c>
       <c r="G99" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H99" t="s">
         <v>822</v>
@@ -10116,13 +10116,13 @@
         <v>307</v>
       </c>
       <c r="E100" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F100" t="s">
         <v>550</v>
       </c>
       <c r="G100" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H100" t="s">
         <v>521</v>
@@ -10136,7 +10136,7 @@
         <v>172</v>
       </c>
       <c r="C101" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D101" t="s">
         <v>308</v>
@@ -10148,7 +10148,7 @@
         <v>551</v>
       </c>
       <c r="G101" t="s">
-        <v>332</v>
+        <v>697</v>
       </c>
       <c r="H101" t="s">
         <v>823</v>
@@ -10162,7 +10162,7 @@
         <v>172</v>
       </c>
       <c r="C102" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D102" t="s">
         <v>308</v>
@@ -10174,7 +10174,7 @@
         <v>552</v>
       </c>
       <c r="G102" t="s">
-        <v>697</v>
+        <v>333</v>
       </c>
       <c r="H102" t="s">
         <v>824</v>
@@ -10240,7 +10240,7 @@
         <v>220</v>
       </c>
       <c r="C105" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D105" t="s">
         <v>307</v>
@@ -10249,10 +10249,10 @@
         <v>406</v>
       </c>
       <c r="F105" t="s">
-        <v>555</v>
+        <v>496</v>
       </c>
       <c r="G105" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="H105" t="s">
         <v>827</v>
@@ -10266,7 +10266,7 @@
         <v>220</v>
       </c>
       <c r="C106" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D106" t="s">
         <v>307</v>
@@ -10275,10 +10275,10 @@
         <v>407</v>
       </c>
       <c r="F106" t="s">
-        <v>494</v>
+        <v>555</v>
       </c>
       <c r="G106" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="H106" t="s">
         <v>828</v>
@@ -10292,19 +10292,19 @@
         <v>220</v>
       </c>
       <c r="C107" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D107" t="s">
         <v>308</v>
       </c>
       <c r="E107" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="F107" t="s">
         <v>556</v>
       </c>
       <c r="G107" t="s">
-        <v>701</v>
+        <v>338</v>
       </c>
       <c r="H107" t="s">
         <v>829</v>
@@ -10324,13 +10324,13 @@
         <v>308</v>
       </c>
       <c r="E108" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F108" t="s">
         <v>557</v>
       </c>
       <c r="G108" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H108" t="s">
         <v>830</v>
@@ -10344,19 +10344,19 @@
         <v>220</v>
       </c>
       <c r="C109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D109" t="s">
         <v>308</v>
       </c>
       <c r="E109" t="s">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="F109" t="s">
         <v>558</v>
       </c>
       <c r="G109" t="s">
-        <v>338</v>
+        <v>702</v>
       </c>
       <c r="H109" t="s">
         <v>831</v>
@@ -10370,7 +10370,7 @@
         <v>172</v>
       </c>
       <c r="C110" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D110" t="s">
         <v>307</v>
@@ -10382,7 +10382,7 @@
         <v>559</v>
       </c>
       <c r="G110" t="s">
-        <v>319</v>
+        <v>703</v>
       </c>
       <c r="H110" t="s">
         <v>832</v>
@@ -10396,7 +10396,7 @@
         <v>172</v>
       </c>
       <c r="C111" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D111" t="s">
         <v>307</v>
@@ -10408,7 +10408,7 @@
         <v>560</v>
       </c>
       <c r="G111" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H111" t="s">
         <v>833</v>
@@ -10422,7 +10422,7 @@
         <v>172</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D112" t="s">
         <v>307</v>
@@ -10434,7 +10434,7 @@
         <v>561</v>
       </c>
       <c r="G112" t="s">
-        <v>704</v>
+        <v>321</v>
       </c>
       <c r="H112" t="s">
         <v>834</v>
@@ -10448,7 +10448,7 @@
         <v>172</v>
       </c>
       <c r="C113" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D113" t="s">
         <v>308</v>
@@ -10460,7 +10460,7 @@
         <v>562</v>
       </c>
       <c r="G113" t="s">
-        <v>705</v>
+        <v>469</v>
       </c>
       <c r="H113" t="s">
         <v>835</v>
@@ -10474,7 +10474,7 @@
         <v>172</v>
       </c>
       <c r="C114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D114" t="s">
         <v>308</v>
@@ -10486,7 +10486,7 @@
         <v>563</v>
       </c>
       <c r="G114" t="s">
-        <v>468</v>
+        <v>705</v>
       </c>
       <c r="H114" t="s">
         <v>836</v>
@@ -10526,7 +10526,7 @@
         <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D116" t="s">
         <v>307</v>
@@ -10541,7 +10541,7 @@
         <v>707</v>
       </c>
       <c r="H116" t="s">
-        <v>838</v>
+        <v>526</v>
       </c>
     </row>
     <row r="117">
@@ -10552,7 +10552,7 @@
         <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D117" t="s">
         <v>307</v>
@@ -10567,7 +10567,7 @@
         <v>708</v>
       </c>
       <c r="H117" t="s">
-        <v>597</v>
+        <v>838</v>
       </c>
     </row>
     <row r="118">
@@ -10578,7 +10578,7 @@
         <v>220</v>
       </c>
       <c r="C118" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D118" t="s">
         <v>307</v>
@@ -10593,7 +10593,7 @@
         <v>709</v>
       </c>
       <c r="H118" t="s">
-        <v>526</v>
+        <v>597</v>
       </c>
     </row>
     <row r="119">
@@ -10604,22 +10604,22 @@
         <v>220</v>
       </c>
       <c r="C119" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D119" t="s">
         <v>308</v>
       </c>
       <c r="E119" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="F119" t="s">
         <v>568</v>
       </c>
       <c r="G119" t="s">
-        <v>467</v>
+        <v>710</v>
       </c>
       <c r="H119" t="s">
-        <v>785</v>
+        <v>839</v>
       </c>
     </row>
     <row r="120">
@@ -10630,22 +10630,22 @@
         <v>220</v>
       </c>
       <c r="C120" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D120" t="s">
         <v>308</v>
       </c>
       <c r="E120" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="F120" t="s">
         <v>569</v>
       </c>
       <c r="G120" t="s">
-        <v>668</v>
+        <v>466</v>
       </c>
       <c r="H120" t="s">
-        <v>418</v>
+        <v>785</v>
       </c>
     </row>
     <row r="121">
@@ -10656,22 +10656,22 @@
         <v>220</v>
       </c>
       <c r="C121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D121" t="s">
         <v>308</v>
       </c>
       <c r="E121" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="F121" t="s">
         <v>570</v>
       </c>
       <c r="G121" t="s">
-        <v>710</v>
+        <v>668</v>
       </c>
       <c r="H121" t="s">
-        <v>839</v>
+        <v>416</v>
       </c>
     </row>
     <row r="122">
@@ -10682,7 +10682,7 @@
         <v>172</v>
       </c>
       <c r="C122" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D122" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>420</v>
       </c>
       <c r="F122" t="s">
-        <v>322</v>
+        <v>571</v>
       </c>
       <c r="G122" t="s">
         <v>711</v>
       </c>
       <c r="H122" t="s">
-        <v>840</v>
+        <v>674</v>
       </c>
     </row>
     <row r="123">
@@ -10717,7 +10717,7 @@
         <v>371</v>
       </c>
       <c r="F123" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G123" t="s">
         <v>712</v>
@@ -10734,7 +10734,7 @@
         <v>172</v>
       </c>
       <c r="C124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D124" t="s">
         <v>307</v>
@@ -10743,13 +10743,13 @@
         <v>421</v>
       </c>
       <c r="F124" t="s">
-        <v>572</v>
+        <v>322</v>
       </c>
       <c r="G124" t="s">
         <v>713</v>
       </c>
       <c r="H124" t="s">
-        <v>674</v>
+        <v>840</v>
       </c>
     </row>
     <row r="125">
@@ -10760,7 +10760,7 @@
         <v>172</v>
       </c>
       <c r="C125" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D125" t="s">
         <v>308</v>
@@ -10786,7 +10786,7 @@
         <v>172</v>
       </c>
       <c r="C126" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D126" t="s">
         <v>308</v>
@@ -10812,7 +10812,7 @@
         <v>172</v>
       </c>
       <c r="C127" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D127" t="s">
         <v>308</v>
@@ -10838,7 +10838,7 @@
         <v>220</v>
       </c>
       <c r="C128" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D128" t="s">
         <v>307</v>
@@ -10850,7 +10850,7 @@
         <v>576</v>
       </c>
       <c r="G128" t="s">
-        <v>717</v>
+        <v>685</v>
       </c>
       <c r="H128" t="s">
         <v>844</v>
@@ -10876,7 +10876,7 @@
         <v>577</v>
       </c>
       <c r="G129" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H129" t="s">
         <v>845</v>
@@ -10890,7 +10890,7 @@
         <v>220</v>
       </c>
       <c r="C130" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D130" t="s">
         <v>307</v>
@@ -10902,7 +10902,7 @@
         <v>578</v>
       </c>
       <c r="G130" t="s">
-        <v>684</v>
+        <v>718</v>
       </c>
       <c r="H130" t="s">
         <v>846</v>
@@ -10916,7 +10916,7 @@
         <v>220</v>
       </c>
       <c r="C131" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D131" t="s">
         <v>308</v>
@@ -10925,13 +10925,13 @@
         <v>428</v>
       </c>
       <c r="F131" t="s">
-        <v>400</v>
+        <v>579</v>
       </c>
       <c r="G131" t="s">
         <v>719</v>
       </c>
       <c r="H131" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
     </row>
     <row r="132">
@@ -10942,7 +10942,7 @@
         <v>220</v>
       </c>
       <c r="C132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D132" t="s">
         <v>308</v>
@@ -10951,13 +10951,13 @@
         <v>429</v>
       </c>
       <c r="F132" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="G132" t="s">
         <v>720</v>
       </c>
       <c r="H132" t="s">
-        <v>646</v>
+        <v>364</v>
       </c>
     </row>
     <row r="133">
@@ -10968,7 +10968,7 @@
         <v>220</v>
       </c>
       <c r="C133" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D133" t="s">
         <v>308</v>
@@ -10977,13 +10977,13 @@
         <v>430</v>
       </c>
       <c r="F133" t="s">
-        <v>579</v>
+        <v>385</v>
       </c>
       <c r="G133" t="s">
         <v>721</v>
       </c>
       <c r="H133" t="s">
-        <v>329</v>
+        <v>645</v>
       </c>
     </row>
     <row r="134">
@@ -10994,13 +10994,13 @@
         <v>172</v>
       </c>
       <c r="C134" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D134" t="s">
         <v>307</v>
       </c>
       <c r="E134" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F134" t="s">
         <v>580</v>
@@ -11009,7 +11009,7 @@
         <v>722</v>
       </c>
       <c r="H134" t="s">
-        <v>847</v>
+        <v>710</v>
       </c>
     </row>
     <row r="135">
@@ -11020,13 +11020,13 @@
         <v>172</v>
       </c>
       <c r="C135" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D135" t="s">
         <v>307</v>
       </c>
       <c r="E135" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F135" t="s">
         <v>581</v>
@@ -11035,7 +11035,7 @@
         <v>723</v>
       </c>
       <c r="H135" t="s">
-        <v>710</v>
+        <v>510</v>
       </c>
     </row>
     <row r="136">
@@ -11046,13 +11046,13 @@
         <v>172</v>
       </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D136" t="s">
         <v>307</v>
       </c>
       <c r="E136" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="F136" t="s">
         <v>582</v>
@@ -11061,7 +11061,7 @@
         <v>724</v>
       </c>
       <c r="H136" t="s">
-        <v>510</v>
+        <v>847</v>
       </c>
     </row>
     <row r="137">
@@ -11072,7 +11072,7 @@
         <v>172</v>
       </c>
       <c r="C137" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D137" t="s">
         <v>308</v>
@@ -11098,7 +11098,7 @@
         <v>172</v>
       </c>
       <c r="C138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D138" t="s">
         <v>308</v>
@@ -11110,10 +11110,10 @@
         <v>584</v>
       </c>
       <c r="G138" t="s">
-        <v>581</v>
+        <v>726</v>
       </c>
       <c r="H138" t="s">
-        <v>794</v>
+        <v>849</v>
       </c>
     </row>
     <row r="139">
@@ -11124,7 +11124,7 @@
         <v>172</v>
       </c>
       <c r="C139" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D139" t="s">
         <v>308</v>
@@ -11136,10 +11136,10 @@
         <v>585</v>
       </c>
       <c r="G139" t="s">
-        <v>726</v>
+        <v>580</v>
       </c>
       <c r="H139" t="s">
-        <v>849</v>
+        <v>794</v>
       </c>
     </row>
     <row r="140">
@@ -11150,7 +11150,7 @@
         <v>220</v>
       </c>
       <c r="C140" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D140" t="s">
         <v>307</v>
@@ -11176,7 +11176,7 @@
         <v>220</v>
       </c>
       <c r="C141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D141" t="s">
         <v>307</v>
@@ -11202,7 +11202,7 @@
         <v>220</v>
       </c>
       <c r="C142" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D142" t="s">
         <v>307</v>
@@ -11228,7 +11228,7 @@
         <v>220</v>
       </c>
       <c r="C143" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D143" t="s">
         <v>308</v>
@@ -11237,13 +11237,13 @@
         <v>439</v>
       </c>
       <c r="F143" t="s">
-        <v>530</v>
+        <v>589</v>
       </c>
       <c r="G143" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H143" t="s">
-        <v>853</v>
+        <v>557</v>
       </c>
     </row>
     <row r="144">
@@ -11263,10 +11263,10 @@
         <v>440</v>
       </c>
       <c r="F144" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G144" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H144" t="s">
         <v>639</v>
@@ -11280,7 +11280,7 @@
         <v>220</v>
       </c>
       <c r="C145" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D145" t="s">
         <v>308</v>
@@ -11289,13 +11289,13 @@
         <v>441</v>
       </c>
       <c r="F145" t="s">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="G145" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="H145" t="s">
-        <v>557</v>
+        <v>853</v>
       </c>
     </row>
     <row r="146">
@@ -11306,7 +11306,7 @@
         <v>172</v>
       </c>
       <c r="C146" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D146" t="s">
         <v>307</v>
@@ -11318,7 +11318,7 @@
         <v>591</v>
       </c>
       <c r="G146" t="s">
-        <v>731</v>
+        <v>659</v>
       </c>
       <c r="H146" t="s">
         <v>854</v>
@@ -11332,7 +11332,7 @@
         <v>172</v>
       </c>
       <c r="C147" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D147" t="s">
         <v>307</v>
@@ -11344,7 +11344,7 @@
         <v>592</v>
       </c>
       <c r="G147" t="s">
-        <v>659</v>
+        <v>731</v>
       </c>
       <c r="H147" t="s">
         <v>855</v>
@@ -11358,7 +11358,7 @@
         <v>172</v>
       </c>
       <c r="C148" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D148" t="s">
         <v>307</v>
@@ -11384,7 +11384,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D149" t="s">
         <v>308</v>
@@ -11396,10 +11396,10 @@
         <v>594</v>
       </c>
       <c r="G149" t="s">
-        <v>733</v>
+        <v>522</v>
       </c>
       <c r="H149" t="s">
-        <v>551</v>
+        <v>832</v>
       </c>
     </row>
     <row r="150">
@@ -11410,7 +11410,7 @@
         <v>172</v>
       </c>
       <c r="C150" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D150" t="s">
         <v>308</v>
@@ -11422,10 +11422,10 @@
         <v>595</v>
       </c>
       <c r="G150" t="s">
-        <v>522</v>
+        <v>733</v>
       </c>
       <c r="H150" t="s">
-        <v>833</v>
+        <v>857</v>
       </c>
     </row>
     <row r="151">
@@ -11436,7 +11436,7 @@
         <v>172</v>
       </c>
       <c r="C151" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D151" t="s">
         <v>308</v>
@@ -11451,7 +11451,7 @@
         <v>734</v>
       </c>
       <c r="H151" t="s">
-        <v>857</v>
+        <v>552</v>
       </c>
     </row>
     <row r="152">
@@ -11540,7 +11540,7 @@
         <v>220</v>
       </c>
       <c r="C155" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D155" t="s">
         <v>308</v>
@@ -11566,7 +11566,7 @@
         <v>220</v>
       </c>
       <c r="C156" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D156" t="s">
         <v>308</v>
@@ -11581,7 +11581,7 @@
         <v>738</v>
       </c>
       <c r="H156" t="s">
-        <v>862</v>
+        <v>352</v>
       </c>
     </row>
     <row r="157">
@@ -11592,7 +11592,7 @@
         <v>220</v>
       </c>
       <c r="C157" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D157" t="s">
         <v>308</v>
@@ -11607,7 +11607,7 @@
         <v>739</v>
       </c>
       <c r="H157" t="s">
-        <v>353</v>
+        <v>862</v>
       </c>
     </row>
     <row r="158">
@@ -11618,7 +11618,7 @@
         <v>172</v>
       </c>
       <c r="C158" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D158" t="s">
         <v>307</v>
@@ -11630,7 +11630,7 @@
         <v>603</v>
       </c>
       <c r="G158" t="s">
-        <v>630</v>
+        <v>732</v>
       </c>
       <c r="H158" t="s">
         <v>863</v>
@@ -11644,7 +11644,7 @@
         <v>172</v>
       </c>
       <c r="C159" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D159" t="s">
         <v>307</v>
@@ -11656,7 +11656,7 @@
         <v>604</v>
       </c>
       <c r="G159" t="s">
-        <v>396</v>
+        <v>630</v>
       </c>
       <c r="H159" t="s">
         <v>864</v>
@@ -11670,7 +11670,7 @@
         <v>172</v>
       </c>
       <c r="C160" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D160" t="s">
         <v>307</v>
@@ -11682,7 +11682,7 @@
         <v>605</v>
       </c>
       <c r="G160" t="s">
-        <v>731</v>
+        <v>396</v>
       </c>
       <c r="H160" t="s">
         <v>865</v>
@@ -11696,7 +11696,7 @@
         <v>172</v>
       </c>
       <c r="C161" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D161" t="s">
         <v>308</v>
@@ -11711,7 +11711,7 @@
         <v>740</v>
       </c>
       <c r="H161" t="s">
-        <v>866</v>
+        <v>779</v>
       </c>
     </row>
     <row r="162">
@@ -11722,7 +11722,7 @@
         <v>172</v>
       </c>
       <c r="C162" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D162" t="s">
         <v>308</v>
@@ -11734,10 +11734,10 @@
         <v>607</v>
       </c>
       <c r="G162" t="s">
-        <v>741</v>
+        <v>585</v>
       </c>
       <c r="H162" t="s">
-        <v>778</v>
+        <v>866</v>
       </c>
     </row>
     <row r="163">
@@ -11748,7 +11748,7 @@
         <v>172</v>
       </c>
       <c r="C163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D163" t="s">
         <v>308</v>
@@ -11760,7 +11760,7 @@
         <v>608</v>
       </c>
       <c r="G163" t="s">
-        <v>584</v>
+        <v>741</v>
       </c>
       <c r="H163" t="s">
         <v>867</v>
@@ -11800,7 +11800,7 @@
         <v>220</v>
       </c>
       <c r="C165" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D165" t="s">
         <v>307</v>
@@ -11812,10 +11812,10 @@
         <v>610</v>
       </c>
       <c r="G165" t="s">
-        <v>318</v>
+        <v>743</v>
       </c>
       <c r="H165" t="s">
-        <v>869</v>
+        <v>810</v>
       </c>
     </row>
     <row r="166">
@@ -11826,7 +11826,7 @@
         <v>220</v>
       </c>
       <c r="C166" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D166" t="s">
         <v>307</v>
@@ -11838,10 +11838,10 @@
         <v>611</v>
       </c>
       <c r="G166" t="s">
-        <v>743</v>
+        <v>318</v>
       </c>
       <c r="H166" t="s">
-        <v>809</v>
+        <v>869</v>
       </c>
     </row>
     <row r="167">
@@ -11852,7 +11852,7 @@
         <v>220</v>
       </c>
       <c r="C167" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D167" t="s">
         <v>308</v>
@@ -11867,7 +11867,7 @@
         <v>744</v>
       </c>
       <c r="H167" t="s">
-        <v>870</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168">
@@ -11878,13 +11878,13 @@
         <v>220</v>
       </c>
       <c r="C168" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D168" t="s">
         <v>308</v>
       </c>
       <c r="E168" t="s">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="F168" t="s">
         <v>613</v>
@@ -11893,7 +11893,7 @@
         <v>745</v>
       </c>
       <c r="H168" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="169">
@@ -11904,13 +11904,13 @@
         <v>220</v>
       </c>
       <c r="C169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D169" t="s">
         <v>308</v>
       </c>
       <c r="E169" t="s">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="F169" t="s">
         <v>614</v>
@@ -11919,7 +11919,7 @@
         <v>746</v>
       </c>
       <c r="H169" t="s">
-        <v>649</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -12189,7 +12189,7 @@
         <v>925</v>
       </c>
       <c r="B3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C3" t="s">
         <v>940</v>
@@ -12246,7 +12246,7 @@
         <v>942</v>
       </c>
       <c r="D6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E6" t="s">
         <v>955</v>
